--- a/Team-Data/2008-09/3-4-2008-09.xlsx
+++ b/Team-Data/2008-09/3-4-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,52 +728,52 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
         <v>34</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J2" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L2" t="n">
         <v>7.4</v>
       </c>
       <c r="M2" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O2" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="P2" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="R2" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S2" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T2" t="n">
         <v>40</v>
@@ -718,28 +785,28 @@
         <v>13.1</v>
       </c>
       <c r="W2" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y2" t="n">
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -754,7 +821,7 @@
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
@@ -769,7 +836,7 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
         <v>16</v>
@@ -784,31 +851,31 @@
         <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX2" t="n">
         <v>16</v>
       </c>
-      <c r="AV2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW2" t="n">
+      <c r="AY2" t="n">
         <v>11</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>10</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB2" t="n">
         <v>18</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -858,43 +925,43 @@
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.488</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
         <v>16.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.395</v>
+        <v>0.389</v>
       </c>
       <c r="O3" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P3" t="n">
         <v>26.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.775</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
         <v>42.6</v>
       </c>
       <c r="U3" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="V3" t="n">
         <v>15.9</v>
@@ -903,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
         <v>4.5</v>
@@ -915,16 +982,16 @@
         <v>22.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.9</v>
+        <v>101.5</v>
       </c>
       <c r="AC3" t="n">
         <v>9.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>3</v>
@@ -933,13 +1000,13 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
         <v>2</v>
@@ -948,28 +1015,28 @@
         <v>16</v>
       </c>
       <c r="AM3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP3" t="n">
         <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
@@ -981,7 +1048,7 @@
         <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
@@ -1112,7 +1179,7 @@
         <v>20</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH4" t="n">
         <v>2</v>
@@ -1142,19 +1209,19 @@
         <v>19</v>
       </c>
       <c r="AQ4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR4" t="n">
         <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
         <v>26</v>
       </c>
       <c r="AU4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV4" t="n">
         <v>25</v>
@@ -1169,10 +1236,10 @@
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -1225,10 +1292,10 @@
         <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L5" t="n">
         <v>5.8</v>
@@ -1237,31 +1304,31 @@
         <v>15.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.375</v>
+        <v>0.373</v>
       </c>
       <c r="O5" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="P5" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.79</v>
+        <v>0.788</v>
       </c>
       <c r="R5" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U5" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
@@ -1276,28 +1343,28 @@
         <v>21.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
         <v>100.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL5" t="n">
         <v>24</v>
@@ -1315,13 +1382,13 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO5" t="n">
         <v>11</v>
       </c>
-      <c r="AO5" t="n">
-        <v>13</v>
-      </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1333,34 +1400,34 @@
         <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ5" t="n">
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB5" t="n">
         <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -1392,13 +1459,13 @@
         <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.797</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
@@ -1407,28 +1474,28 @@
         <v>36.8</v>
       </c>
       <c r="J6" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K6" t="n">
         <v>0.47</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
         <v>20.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.391</v>
+        <v>0.387</v>
       </c>
       <c r="O6" t="n">
         <v>18.6</v>
       </c>
       <c r="P6" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R6" t="n">
         <v>10.8</v>
@@ -1443,10 +1510,10 @@
         <v>20</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X6" t="n">
         <v>5.6</v>
@@ -1455,34 +1522,34 @@
         <v>4.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1500,7 +1567,7 @@
         <v>4</v>
       </c>
       <c r="AO6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1509,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1518,10 +1585,10 @@
         <v>12</v>
       </c>
       <c r="AU6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW6" t="n">
         <v>8</v>
@@ -1530,10 +1597,10 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA6" t="n">
         <v>21</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" t="n">
         <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>0.607</v>
+        <v>0.6</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
@@ -1589,49 +1656,49 @@
         <v>38.1</v>
       </c>
       <c r="J7" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L7" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M7" t="n">
         <v>19.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O7" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P7" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.819</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S7" t="n">
         <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="U7" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V7" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W7" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y7" t="n">
         <v>4.1</v>
@@ -1640,19 +1707,19 @@
         <v>19.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>101</v>
+        <v>100.9</v>
       </c>
       <c r="AC7" t="n">
         <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF7" t="n">
         <v>11</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1673,13 +1740,13 @@
         <v>10</v>
       </c>
       <c r="AL7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM7" t="n">
         <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO7" t="n">
         <v>24</v>
@@ -1691,28 +1758,28 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
         <v>4</v>
       </c>
       <c r="AU7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>3</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -1831,22 +1898,22 @@
         <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AJ8" t="n">
         <v>24</v>
@@ -1861,7 +1928,7 @@
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1894,10 +1961,10 @@
         <v>3</v>
       </c>
       <c r="AY8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
         <v>15</v>
@@ -2034,16 +2101,16 @@
         <v>22</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM9" t="n">
         <v>28</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
         <v>27</v>
@@ -2052,7 +2119,7 @@
         <v>24</v>
       </c>
       <c r="AQ9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR9" t="n">
         <v>17</v>
@@ -2061,7 +2128,7 @@
         <v>19</v>
       </c>
       <c r="AT9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
         <v>23</v>
@@ -2073,7 +2140,7 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY9" t="n">
         <v>4</v>
@@ -2085,7 +2152,7 @@
         <v>24</v>
       </c>
       <c r="BB9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC9" t="n">
         <v>17</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -2117,46 +2184,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
         <v>21</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>0.344</v>
+        <v>0.35</v>
       </c>
       <c r="H10" t="n">
         <v>48.6</v>
       </c>
       <c r="I10" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="J10" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L10" t="n">
         <v>6.7</v>
       </c>
       <c r="M10" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.373</v>
+        <v>0.375</v>
       </c>
       <c r="O10" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="P10" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.782</v>
+        <v>0.781</v>
       </c>
       <c r="R10" t="n">
         <v>11.6</v>
@@ -2168,13 +2235,13 @@
         <v>41.7</v>
       </c>
       <c r="U10" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X10" t="n">
         <v>6.5</v>
@@ -2186,28 +2253,28 @@
         <v>22.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>107.9</v>
+        <v>108.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.4</v>
+        <v>-3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2219,13 +2286,13 @@
         <v>11</v>
       </c>
       <c r="AL10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM10" t="n">
         <v>17</v>
       </c>
       <c r="AN10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -2258,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ10" t="n">
         <v>24</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
         <v>39</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>0.629</v>
+        <v>0.639</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J11" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K11" t="n">
         <v>0.449</v>
@@ -2335,25 +2402,25 @@
         <v>19.4</v>
       </c>
       <c r="P11" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S11" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="T11" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="U11" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V11" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W11" t="n">
         <v>6.8</v>
@@ -2368,49 +2435,49 @@
         <v>18.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ11" t="n">
         <v>20</v>
       </c>
       <c r="AK11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM11" t="n">
         <v>5</v>
       </c>
       <c r="AN11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2425,13 +2492,13 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
         <v>26</v>
@@ -2446,13 +2513,13 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BB11" t="n">
         <v>17</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -2481,58 +2548,58 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" t="n">
         <v>27</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>0.422</v>
+        <v>0.429</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J12" t="n">
         <v>86.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="N12" t="n">
         <v>0.376</v>
       </c>
       <c r="O12" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P12" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.805</v>
+        <v>0.806</v>
       </c>
       <c r="R12" t="n">
         <v>11.4</v>
       </c>
       <c r="S12" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T12" t="n">
         <v>43.7</v>
       </c>
       <c r="U12" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V12" t="n">
         <v>15</v>
@@ -2544,13 +2611,13 @@
         <v>5.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
         <v>23.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB12" t="n">
         <v>104.8</v>
@@ -2568,7 +2635,7 @@
         <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH12" t="n">
         <v>8</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="n">
         <v>4</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
         <v>17</v>
@@ -2613,16 +2680,16 @@
         <v>5</v>
       </c>
       <c r="AV12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW12" t="n">
         <v>21</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>20</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
@@ -2634,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" t="n">
         <v>15</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>0.242</v>
+        <v>0.246</v>
       </c>
       <c r="H13" t="n">
         <v>48.6</v>
@@ -2681,37 +2748,37 @@
         <v>35.8</v>
       </c>
       <c r="J13" t="n">
-        <v>82</v>
+        <v>82.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L13" t="n">
         <v>6.4</v>
       </c>
       <c r="M13" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O13" t="n">
         <v>16.9</v>
       </c>
       <c r="P13" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="R13" t="n">
         <v>11.2</v>
       </c>
       <c r="S13" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="T13" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U13" t="n">
         <v>21</v>
@@ -2729,22 +2796,22 @@
         <v>5.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB13" t="n">
         <v>94.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.9</v>
+        <v>-8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AF13" t="n">
         <v>28</v>
@@ -2753,10 +2820,10 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2768,37 +2835,37 @@
         <v>18</v>
       </c>
       <c r="AM13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AR13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>22</v>
       </c>
       <c r="AU13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2807,7 +2874,7 @@
         <v>22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
         <v>12</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8</v>
+        <v>0.803</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,7 +2930,7 @@
         <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K14" t="n">
         <v>0.476</v>
@@ -2872,34 +2939,34 @@
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.361</v>
+        <v>0.364</v>
       </c>
       <c r="O14" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="P14" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0.77</v>
       </c>
       <c r="R14" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T14" t="n">
         <v>44.5</v>
       </c>
       <c r="U14" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W14" t="n">
         <v>8.6</v>
@@ -2908,34 +2975,34 @@
         <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.9</v>
+        <v>108.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2947,16 +3014,16 @@
         <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP14" t="n">
         <v>6</v>
@@ -2965,7 +3032,7 @@
         <v>16</v>
       </c>
       <c r="AR14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS14" t="n">
         <v>7</v>
@@ -2986,7 +3053,7 @@
         <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
         <v>14</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -3027,46 +3094,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F15" t="n">
         <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>0.267</v>
+        <v>0.254</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="J15" t="n">
         <v>77.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="L15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
         <v>13.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.339</v>
+        <v>0.336</v>
       </c>
       <c r="O15" t="n">
         <v>19.2</v>
       </c>
       <c r="P15" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R15" t="n">
         <v>10.6</v>
@@ -3075,37 +3142,37 @@
         <v>28.7</v>
       </c>
       <c r="T15" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="U15" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="V15" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W15" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z15" t="n">
         <v>22.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3126,7 +3193,7 @@
         <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3144,16 +3211,16 @@
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR15" t="n">
         <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
@@ -3162,22 +3229,22 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX15" t="n">
         <v>21</v>
       </c>
       <c r="AY15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -3209,46 +3276,46 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16" t="n">
         <v>28</v>
       </c>
       <c r="G16" t="n">
-        <v>0.533</v>
+        <v>0.525</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J16" t="n">
         <v>81</v>
       </c>
       <c r="K16" t="n">
-        <v>0.454</v>
+        <v>0.452</v>
       </c>
       <c r="L16" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M16" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.352</v>
+        <v>0.348</v>
       </c>
       <c r="O16" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="P16" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.755</v>
+        <v>0.752</v>
       </c>
       <c r="R16" t="n">
         <v>10.2</v>
@@ -3260,10 +3327,10 @@
         <v>39.3</v>
       </c>
       <c r="U16" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="V16" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="W16" t="n">
         <v>8.1</v>
@@ -3278,16 +3345,16 @@
         <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3302,31 +3369,31 @@
         <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AJ16" t="n">
         <v>12</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM16" t="n">
         <v>10</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP16" t="n">
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR16" t="n">
         <v>25</v>
@@ -3338,28 +3405,28 @@
         <v>29</v>
       </c>
       <c r="AU16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY16" t="n">
         <v>5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
         <v>27</v>
       </c>
       <c r="BB16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -3406,49 +3473,49 @@
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J17" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M17" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.363</v>
+        <v>0.366</v>
       </c>
       <c r="O17" t="n">
         <v>20.3</v>
       </c>
       <c r="P17" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.782</v>
+        <v>0.78</v>
       </c>
       <c r="R17" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.1</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X17" t="n">
         <v>3.8</v>
@@ -3457,25 +3524,25 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
         <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.3</v>
+        <v>99.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3484,28 +3551,28 @@
         <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ17" t="n">
         <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
         <v>21</v>
       </c>
       <c r="AM17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
@@ -3514,16 +3581,16 @@
         <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU17" t="n">
         <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
         <v>15</v>
@@ -3532,7 +3599,7 @@
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3541,7 +3608,7 @@
         <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC17" t="n">
         <v>15</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-4.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,7 +3730,7 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI18" t="n">
         <v>11</v>
@@ -3687,7 +3754,7 @@
         <v>18</v>
       </c>
       <c r="AP18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
         <v>17</v>
@@ -3702,10 +3769,10 @@
         <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3717,13 +3784,13 @@
         <v>30</v>
       </c>
       <c r="AZ18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA18" t="n">
         <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
         <v>27</v>
       </c>
       <c r="F19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G19" t="n">
-        <v>0.443</v>
+        <v>0.45</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
@@ -3773,19 +3840,19 @@
         <v>35.6</v>
       </c>
       <c r="J19" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L19" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M19" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O19" t="n">
         <v>19.3</v>
@@ -3794,19 +3861,19 @@
         <v>24.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.786</v>
+        <v>0.784</v>
       </c>
       <c r="R19" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S19" t="n">
-        <v>29.4</v>
+        <v>29.6</v>
       </c>
       <c r="T19" t="n">
-        <v>40.3</v>
+        <v>40.5</v>
       </c>
       <c r="U19" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V19" t="n">
         <v>13.3</v>
@@ -3815,25 +3882,25 @@
         <v>7</v>
       </c>
       <c r="X19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="AC19" t="n">
         <v>-2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3857,19 +3924,19 @@
         <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM19" t="n">
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
         <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
         <v>9</v>
@@ -3878,10 +3945,10 @@
         <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU19" t="n">
         <v>28</v>
@@ -3893,19 +3960,19 @@
         <v>23</v>
       </c>
       <c r="AX19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY19" t="n">
         <v>17</v>
       </c>
       <c r="AZ19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -4015,16 +4082,16 @@
         <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH20" t="n">
         <v>28</v>
@@ -4033,7 +4100,7 @@
         <v>28</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK20" t="n">
         <v>14</v>
@@ -4045,10 +4112,10 @@
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP20" t="n">
         <v>22</v>
@@ -4072,16 +4139,16 @@
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
       </c>
       <c r="AZ20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA20" t="n">
         <v>15</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F21" t="n">
         <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>0.417</v>
+        <v>0.407</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4146,37 +4213,37 @@
         <v>10.5</v>
       </c>
       <c r="M21" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.366</v>
+        <v>0.365</v>
       </c>
       <c r="O21" t="n">
         <v>18.1</v>
       </c>
       <c r="P21" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.794</v>
+        <v>0.793</v>
       </c>
       <c r="R21" t="n">
         <v>11.1</v>
       </c>
       <c r="S21" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T21" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U21" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V21" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W21" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X21" t="n">
         <v>2.4</v>
@@ -4191,13 +4258,13 @@
         <v>19.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>106.1</v>
+        <v>106</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO21" t="n">
         <v>23</v>
@@ -4245,16 +4312,16 @@
         <v>8</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW21" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>0.262</v>
+        <v>0.25</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,28 +4386,28 @@
         <v>36.9</v>
       </c>
       <c r="J22" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K22" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M22" t="n">
         <v>11.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O22" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="P22" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.778</v>
+        <v>0.78</v>
       </c>
       <c r="R22" t="n">
         <v>12.4</v>
@@ -4364,22 +4431,22 @@
         <v>4.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z22" t="n">
         <v>20.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB22" t="n">
-        <v>98.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>-5.6</v>
+        <v>-5.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>26</v>
@@ -4391,7 +4458,7 @@
         <v>27</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI22" t="n">
         <v>12</v>
@@ -4412,10 +4479,10 @@
         <v>15</v>
       </c>
       <c r="AO22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP22" t="n">
         <v>9</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>10</v>
       </c>
       <c r="AQ22" t="n">
         <v>12</v>
@@ -4430,7 +4497,7 @@
         <v>3</v>
       </c>
       <c r="AU22" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4445,13 +4512,13 @@
         <v>18</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BB22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>7</v>
       </c>
       <c r="AD23" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4591,7 +4658,7 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO23" t="n">
         <v>10</v>
@@ -4609,7 +4676,7 @@
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU23" t="n">
         <v>29</v>
@@ -4627,7 +4694,7 @@
         <v>3</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA23" t="n">
         <v>8</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
         <v>16</v>
@@ -4776,31 +4843,31 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP24" t="n">
         <v>8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS24" t="n">
         <v>18</v>
       </c>
       <c r="AT24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
         <v>21</v>
       </c>
       <c r="AV24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX24" t="n">
         <v>8</v>
@@ -4809,7 +4876,7 @@
         <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -4847,37 +4914,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25" t="n">
         <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="J25" t="n">
-        <v>79.8</v>
+        <v>79.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.502</v>
+        <v>0.501</v>
       </c>
       <c r="L25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0.384</v>
+        <v>0.381</v>
       </c>
       <c r="O25" t="n">
         <v>20.8</v>
@@ -4886,16 +4953,16 @@
         <v>27.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.758</v>
+        <v>0.76</v>
       </c>
       <c r="R25" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S25" t="n">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="T25" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="U25" t="n">
         <v>22.6</v>
@@ -4919,13 +4986,13 @@
         <v>22.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>107.4</v>
+        <v>107</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
@@ -4937,13 +5004,13 @@
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
@@ -4955,7 +5022,7 @@
         <v>19</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>4</v>
@@ -4982,7 +5049,7 @@
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -4991,7 +5058,7 @@
         <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA25" t="n">
         <v>5</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -5032,55 +5099,55 @@
         <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G26" t="n">
-        <v>0.644</v>
+        <v>0.627</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
         <v>79.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.764</v>
+        <v>0.76</v>
       </c>
       <c r="R26" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S26" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="T26" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U26" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V26" t="n">
         <v>12.9</v>
@@ -5098,16 +5165,16 @@
         <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.5</v>
+        <v>99</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
@@ -5116,31 +5183,31 @@
         <v>6</v>
       </c>
       <c r="AG26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH26" t="n">
         <v>14</v>
       </c>
       <c r="AI26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
       </c>
       <c r="AM26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
@@ -5158,7 +5225,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5167,7 +5234,7 @@
         <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY26" t="n">
         <v>2</v>
@@ -5176,10 +5243,10 @@
         <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -5301,10 +5368,10 @@
         <v>30</v>
       </c>
       <c r="AH27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ27" t="n">
         <v>13</v>
@@ -5322,7 +5389,7 @@
         <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP27" t="n">
         <v>12</v>
@@ -5346,13 +5413,13 @@
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX27" t="n">
         <v>26</v>
       </c>
       <c r="AY27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
@@ -5361,7 +5428,7 @@
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -5393,25 +5460,25 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E28" t="n">
         <v>40</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G28" t="n">
-        <v>0.667</v>
+        <v>0.678</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J28" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K28" t="n">
         <v>0.464</v>
@@ -5420,13 +5487,13 @@
         <v>7.9</v>
       </c>
       <c r="M28" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
       <c r="O28" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P28" t="n">
         <v>19.9</v>
@@ -5435,10 +5502,10 @@
         <v>0.772</v>
       </c>
       <c r="R28" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="T28" t="n">
         <v>41</v>
@@ -5447,7 +5514,7 @@
         <v>21.8</v>
       </c>
       <c r="V28" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="W28" t="n">
         <v>5.8</v>
@@ -5465,13 +5532,13 @@
         <v>18.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.40000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5492,7 +5559,7 @@
         <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
         <v>5</v>
@@ -5501,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5519,7 +5586,7 @@
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
@@ -5531,10 +5598,10 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5543,10 +5610,10 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -5665,13 +5732,13 @@
         <v>23</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
         <v>19</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK29" t="n">
         <v>13</v>
@@ -5686,7 +5753,7 @@
         <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP29" t="n">
         <v>27</v>
@@ -5701,13 +5768,13 @@
         <v>12</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
         <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>29</v>
@@ -5716,7 +5783,7 @@
         <v>13</v>
       </c>
       <c r="AY29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ29" t="n">
         <v>4</v>
@@ -5725,7 +5792,7 @@
         <v>23</v>
       </c>
       <c r="BB29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC29" t="n">
         <v>24</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F30" t="n">
         <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>0.623</v>
+        <v>0.617</v>
       </c>
       <c r="H30" t="n">
         <v>48.3</v>
@@ -5778,55 +5845,55 @@
         <v>79.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.48</v>
+        <v>0.479</v>
       </c>
       <c r="L30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M30" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O30" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="P30" t="n">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="R30" t="n">
         <v>11.6</v>
       </c>
       <c r="S30" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T30" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U30" t="n">
         <v>24.9</v>
       </c>
       <c r="V30" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W30" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y30" t="n">
         <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AB30" t="n">
         <v>103.1</v>
@@ -5835,19 +5902,19 @@
         <v>3.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE30" t="n">
         <v>8</v>
       </c>
       <c r="AF30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG30" t="n">
         <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
@@ -5889,19 +5956,19 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
         <v>16</v>
       </c>
       <c r="AZ30" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA30" t="n">
         <v>1</v>
@@ -5910,7 +5977,7 @@
         <v>6</v>
       </c>
       <c r="BC30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
@@ -5939,64 +6006,64 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
         <v>14</v>
       </c>
       <c r="F31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G31" t="n">
-        <v>0.23</v>
+        <v>0.233</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.1</v>
+        <v>36.3</v>
       </c>
       <c r="J31" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L31" t="n">
         <v>4.9</v>
       </c>
       <c r="M31" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="N31" t="n">
         <v>0.322</v>
       </c>
       <c r="O31" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P31" t="n">
         <v>22.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R31" t="n">
         <v>11.9</v>
       </c>
       <c r="S31" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="T31" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="U31" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V31" t="n">
         <v>14</v>
       </c>
       <c r="W31" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X31" t="n">
         <v>4.2</v>
@@ -6005,19 +6072,19 @@
         <v>5.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
         <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>94.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.4</v>
+        <v>-7.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6053,7 +6120,7 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ31" t="n">
         <v>18</v>
@@ -6065,7 +6132,7 @@
         <v>30</v>
       </c>
       <c r="AT31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU31" t="n">
         <v>22</v>
@@ -6083,7 +6150,7 @@
         <v>21</v>
       </c>
       <c r="AZ31" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BA31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-4-2008-09</t>
+          <t>2009-03-04</t>
         </is>
       </c>
     </row>
